--- a/data/cpi.xlsx
+++ b/data/cpi.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" customWidth="1" min="1" max="1"/>
@@ -434,11 +434,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -448,11 +448,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -462,11 +462,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -476,11 +476,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -490,11 +490,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -504,11 +504,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -518,11 +518,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -532,11 +532,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -546,11 +546,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.32</v>
+        <v>1.74</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -560,11 +560,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -574,11 +574,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -588,11 +588,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -602,11 +602,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -614,11 +614,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>2.02</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.89</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -627,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -639,10 +641,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -651,10 +653,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -663,10 +665,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -675,10 +677,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -687,10 +689,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -699,10 +701,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -711,10 +713,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -723,10 +725,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -735,10 +737,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -747,10 +749,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -759,7 +761,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>3.12</v>
@@ -771,10 +773,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -783,10 +785,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -795,10 +797,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -807,10 +809,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -819,10 +821,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -831,10 +833,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>4.41</v>
+        <v>3.36</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -843,10 +845,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>4.3</v>
+        <v>4.41</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -855,10 +857,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>5.25</v>
+        <v>4.3</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -867,10 +869,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>5.92</v>
+        <v>5.25</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -879,10 +881,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>6.32</v>
+        <v>5.92</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -891,10 +893,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>6.8</v>
+        <v>6.32</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -903,10 +905,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -915,10 +917,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -927,10 +929,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>7.01</v>
+        <v>6.86</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -939,10 +941,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>7.59</v>
+        <v>7.01</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -951,10 +953,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -963,10 +965,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>7.73</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -975,10 +977,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>6.77</v>
+        <v>7.73</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -987,10 +989,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>6.66</v>
+        <v>6.77</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -999,10 +1001,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>5.69</v>
+        <v>6.66</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1011,10 +1013,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.14</v>
+        <v>5.69</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1023,10 +1025,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>4.8</v>
+        <v>5.14</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1035,10 +1037,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1047,10 +1049,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1059,10 +1061,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1071,10 +1073,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>4.09</v>
+        <v>4.38</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1083,10 +1085,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>3.72</v>
+        <v>4.09</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1095,10 +1097,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>3.06</v>
+        <v>3.72</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1107,10 +1109,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1119,10 +1121,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1131,10 +1133,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>2.2</v>
+        <v>3.39</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1143,10 +1145,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1155,10 +1157,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1167,10 +1169,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0.73</v>
+        <v>1.02</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1179,10 +1181,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1191,13 +1193,25 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B63" s="3" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C64">
+        <f>(B64/B76-1)*100</f>
         <v/>
       </c>
     </row>

--- a/data/cpi.xlsx
+++ b/data/cpi.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" customWidth="1" min="1" max="1"/>
@@ -434,11 +434,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.78</v>
+        <v>2.39</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -448,11 +448,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -462,11 +462,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -476,11 +476,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -490,11 +490,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -504,11 +504,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -518,11 +518,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -532,11 +532,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -546,11 +546,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -560,11 +560,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.32</v>
+        <v>1.74</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -574,11 +574,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -588,11 +588,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -602,11 +602,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -616,11 +616,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -628,11 +628,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>2.02</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.89</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -641,10 +643,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -653,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -665,10 +667,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -677,10 +679,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -689,10 +691,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -701,10 +703,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -713,10 +715,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -725,10 +727,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -737,10 +739,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -749,10 +751,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -761,10 +763,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -773,7 +775,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>3.12</v>
@@ -785,10 +787,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -797,10 +799,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -809,10 +811,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -821,10 +823,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -833,10 +835,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -845,10 +847,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>4.41</v>
+        <v>3.36</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -857,10 +859,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>4.3</v>
+        <v>4.41</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -869,10 +871,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>5.25</v>
+        <v>4.3</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -881,10 +883,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>5.92</v>
+        <v>5.25</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -893,10 +895,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>6.32</v>
+        <v>5.92</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -905,10 +907,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>6.8</v>
+        <v>6.32</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -917,10 +919,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -929,10 +931,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -941,10 +943,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>7.01</v>
+        <v>6.86</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -953,10 +955,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>7.59</v>
+        <v>7.01</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -965,10 +967,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -977,10 +979,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>7.73</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -989,10 +991,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>6.77</v>
+        <v>7.73</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1001,10 +1003,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>6.66</v>
+        <v>6.77</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1013,10 +1015,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.69</v>
+        <v>6.66</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1025,10 +1027,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>5.14</v>
+        <v>5.69</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1037,10 +1039,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>4.8</v>
+        <v>5.14</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1049,10 +1051,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1061,10 +1063,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1073,10 +1075,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1085,10 +1087,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>4.09</v>
+        <v>4.38</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1097,10 +1099,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>3.72</v>
+        <v>4.09</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1109,10 +1111,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>3.06</v>
+        <v>3.72</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1121,10 +1123,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1133,10 +1135,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1145,10 +1147,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>2.2</v>
+        <v>3.39</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1157,10 +1159,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1169,10 +1171,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1181,10 +1183,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>0.73</v>
+        <v>1.02</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1193,10 +1195,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B63" s="3" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1205,13 +1207,25 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C65">
+        <f>(B65/B77-1)*100</f>
         <v/>
       </c>
     </row>

--- a/data/cpi.xlsx
+++ b/data/cpi.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" customWidth="1" min="1" max="1"/>
@@ -434,11 +434,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.39</v>
+        <v>2.82</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -448,11 +448,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.78</v>
+        <v>2.39</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -462,11 +462,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -476,11 +476,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -490,11 +490,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -504,11 +504,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -518,11 +518,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -532,11 +532,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -546,11 +546,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -560,11 +560,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -574,11 +574,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.32</v>
+        <v>1.74</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -588,11 +588,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -602,11 +602,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -616,11 +616,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -630,11 +630,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -642,11 +642,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>2.02</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.89</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -655,10 +657,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -667,10 +669,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -679,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -691,10 +693,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -703,10 +705,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -715,10 +717,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -727,10 +729,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -739,10 +741,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -751,10 +753,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -763,10 +765,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -775,10 +777,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -787,7 +789,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>3.12</v>
@@ -799,10 +801,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -811,10 +813,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -823,10 +825,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -835,10 +837,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -847,10 +849,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -859,10 +861,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>4.41</v>
+        <v>3.36</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -871,10 +873,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>4.3</v>
+        <v>4.41</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -883,10 +885,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>5.25</v>
+        <v>4.3</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -895,10 +897,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>5.92</v>
+        <v>5.25</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -907,10 +909,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>6.32</v>
+        <v>5.92</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -919,10 +921,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>6.8</v>
+        <v>6.32</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -931,10 +933,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -943,10 +945,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -955,10 +957,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>7.01</v>
+        <v>6.86</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -967,10 +969,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>7.59</v>
+        <v>7.01</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -979,10 +981,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -991,10 +993,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>7.73</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1003,10 +1005,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>6.77</v>
+        <v>7.73</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1015,10 +1017,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.66</v>
+        <v>6.77</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1027,10 +1029,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>5.69</v>
+        <v>6.66</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1039,10 +1041,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>5.14</v>
+        <v>5.69</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1051,10 +1053,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>4.8</v>
+        <v>5.14</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1063,10 +1065,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1075,10 +1077,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1087,10 +1089,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1099,10 +1101,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>4.09</v>
+        <v>4.38</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1111,10 +1113,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>3.72</v>
+        <v>4.09</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1123,10 +1125,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>3.06</v>
+        <v>3.72</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1135,10 +1137,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1147,10 +1149,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1159,10 +1161,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>2.2</v>
+        <v>3.39</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1171,10 +1173,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1183,10 +1185,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1195,10 +1197,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B63" s="3" t="n">
-        <v>0.73</v>
+        <v>1.02</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1207,10 +1209,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1219,13 +1221,25 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B65" s="3" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C66">
+        <f>(B66/B78-1)*100</f>
         <v/>
       </c>
     </row>

--- a/data/cpi.xlsx
+++ b/data/cpi.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" customWidth="1" min="1" max="1"/>
@@ -434,11 +434,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.82</v>
+        <v>3.23</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -448,11 +448,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.39</v>
+        <v>2.82</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -462,11 +462,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.78</v>
+        <v>2.39</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -476,11 +476,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -490,11 +490,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -504,11 +504,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -518,11 +518,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -532,11 +532,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -546,11 +546,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -560,11 +560,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -574,11 +574,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -588,11 +588,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.32</v>
+        <v>1.74</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -602,11 +602,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -616,11 +616,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -630,11 +630,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -644,11 +644,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -656,11 +656,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>2.02</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.89</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -669,10 +671,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -681,10 +683,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -693,10 +695,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -705,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -717,10 +719,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -729,10 +731,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -741,10 +743,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -753,10 +755,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -765,10 +767,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -777,10 +779,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -789,10 +791,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -801,7 +803,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>3.12</v>
@@ -813,10 +815,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -825,10 +827,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -837,10 +839,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -849,10 +851,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -861,10 +863,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -873,10 +875,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>4.41</v>
+        <v>3.36</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -885,10 +887,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>4.3</v>
+        <v>4.41</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -897,10 +899,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>5.25</v>
+        <v>4.3</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -909,10 +911,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>5.92</v>
+        <v>5.25</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -921,10 +923,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>6.32</v>
+        <v>5.92</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -933,10 +935,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>6.8</v>
+        <v>6.32</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -945,10 +947,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -957,10 +959,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -969,10 +971,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>7.01</v>
+        <v>6.86</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -981,10 +983,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>7.59</v>
+        <v>7.01</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -993,10 +995,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1005,10 +1007,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>7.73</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1017,10 +1019,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.77</v>
+        <v>7.73</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1029,10 +1031,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>6.66</v>
+        <v>6.77</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1041,10 +1043,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>5.69</v>
+        <v>6.66</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1053,10 +1055,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>5.14</v>
+        <v>5.69</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1065,10 +1067,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>4.8</v>
+        <v>5.14</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1077,10 +1079,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1089,10 +1091,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1101,10 +1103,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1113,10 +1115,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>4.09</v>
+        <v>4.38</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1125,10 +1127,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>3.72</v>
+        <v>4.09</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1137,10 +1139,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>3.06</v>
+        <v>3.72</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1149,10 +1151,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1161,10 +1163,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1173,10 +1175,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>2.2</v>
+        <v>3.39</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1185,10 +1187,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1197,10 +1199,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B63" s="3" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1209,10 +1211,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0.73</v>
+        <v>1.02</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1221,10 +1223,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B65" s="3" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1233,13 +1235,25 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C67">
+        <f>(B67/B79-1)*100</f>
         <v/>
       </c>
     </row>

--- a/data/cpi.xlsx
+++ b/data/cpi.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" customWidth="1" min="1" max="1"/>
@@ -434,11 +434,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -448,11 +448,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.82</v>
+        <v>3.23</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -462,11 +462,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.39</v>
+        <v>2.82</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -476,11 +476,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.78</v>
+        <v>2.39</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -490,11 +490,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -504,11 +504,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -518,11 +518,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -532,11 +532,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -546,11 +546,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -560,11 +560,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -574,11 +574,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -588,11 +588,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -602,11 +602,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.32</v>
+        <v>1.74</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -616,11 +616,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -630,11 +630,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -644,11 +644,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -658,11 +658,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -670,11 +670,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>2.02</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.89</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -683,10 +685,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -695,10 +697,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -707,10 +709,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -719,10 +721,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -731,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -743,10 +745,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -755,10 +757,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -767,10 +769,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -779,10 +781,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -791,10 +793,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -803,10 +805,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -815,7 +817,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>3.12</v>
@@ -827,10 +829,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -839,10 +841,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -851,10 +853,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -863,10 +865,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -875,10 +877,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -887,10 +889,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>4.41</v>
+        <v>3.36</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -899,10 +901,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>4.3</v>
+        <v>4.41</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -911,10 +913,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>5.25</v>
+        <v>4.3</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -923,10 +925,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>5.92</v>
+        <v>5.25</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -935,10 +937,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>6.32</v>
+        <v>5.92</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -947,10 +949,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>6.8</v>
+        <v>6.32</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -959,10 +961,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -971,10 +973,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -983,10 +985,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>7.01</v>
+        <v>6.86</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -995,10 +997,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>7.59</v>
+        <v>7.01</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1007,10 +1009,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1019,10 +1021,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>7.73</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1031,10 +1033,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>6.77</v>
+        <v>7.73</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1043,10 +1045,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>6.66</v>
+        <v>6.77</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1055,10 +1057,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>5.69</v>
+        <v>6.66</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1067,10 +1069,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>5.14</v>
+        <v>5.69</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1079,10 +1081,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>4.8</v>
+        <v>5.14</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1091,10 +1093,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1103,10 +1105,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1115,10 +1117,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1127,10 +1129,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>4.09</v>
+        <v>4.38</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1139,10 +1141,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>3.72</v>
+        <v>4.09</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1151,10 +1153,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>3.06</v>
+        <v>3.72</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1163,10 +1165,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1175,10 +1177,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1187,10 +1189,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>2.2</v>
+        <v>3.39</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1199,10 +1201,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B63" s="3" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1211,10 +1213,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B64" s="3" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1223,10 +1225,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B65" s="3" t="n">
-        <v>0.73</v>
+        <v>1.02</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1235,10 +1237,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
@@ -1247,13 +1249,25 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="C67">
         <f>(B67/B79-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C68">
+        <f>(B68/B80-1)*100</f>
         <v/>
       </c>
     </row>
